--- a/Team_CamGiang_Report_Updated.xlsx
+++ b/Team_CamGiang_Report_Updated.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiến độ Team" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chi tiết CVS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Data BHX" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Chi tiết SKU FamilyMart" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiến độ Team" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chi tiết CVS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data BHX" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chi tiết SKU FamilyMart" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Chi tiết SKU FamilyMart'!$A$5:$BB$40</definedName>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -695,6 +695,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1098,8 +1101,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1193,20 +1196,23 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
+      <c r="A7" t="n">
+        <v>12299713233</v>
+      </c>
       <c r="B7" s="12" t="n">
-        <v>10826339729</v>
+        <v>3838609228</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>3551927443</v>
+        <v>359247028</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>359247028</v>
+        <v>4197856256</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>3911174471</v>
+        <v>8101856977</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>6915165258</v>
+        <v>0.3412970836374621</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>0.3612647089323572</v>
@@ -1273,19 +1279,19 @@
         </is>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1346491228</v>
+        <v>1427158977</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>498866214</v>
+        <v>462947847</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>498866214</v>
+        <v>462947847</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>0.3704934749118172</v>
+        <v>0.3243842167977338</v>
       </c>
     </row>
     <row r="14">
@@ -1298,19 +1304,19 @@
         </is>
       </c>
       <c r="D14" s="19" t="n">
-        <v>1292631579</v>
+        <v>1490030916</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>478911565</v>
+        <v>501526834</v>
       </c>
       <c r="F14" s="19" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>478911565</v>
+        <v>501526834</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>0.370493474537032</v>
+        <v>0.3365882067375842</v>
       </c>
     </row>
     <row r="15">
@@ -1323,19 +1329,19 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>1354847566</v>
+        <v>1553803206</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>498866214</v>
+        <v>520816327</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>2270422</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>501136636</v>
+        <v>523086749</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>0.3698841468044531</v>
+        <v>0.3366492918666304</v>
       </c>
     </row>
     <row r="16">
@@ -1348,19 +1354,19 @@
         </is>
       </c>
       <c r="D16" s="19" t="n">
-        <v>1399499656</v>
+        <v>1439209643</v>
       </c>
       <c r="E16" s="19" t="n">
-        <v>498866214</v>
+        <v>462947847</v>
       </c>
       <c r="F16" s="19" t="n">
         <v>15438632</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>514304846</v>
+        <v>478386479</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>0.367491941705772</v>
+        <v>0.3323952707840493</v>
       </c>
     </row>
     <row r="17">
@@ -1373,19 +1379,19 @@
         </is>
       </c>
       <c r="D17" s="19" t="n">
-        <v>1181190660</v>
+        <v>1224747376</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>419047620</v>
+        <v>405079366</v>
       </c>
       <c r="F17" s="19" t="n">
         <v>13622532</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>432670152</v>
+        <v>418701898</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>0.3663000112107219</v>
+        <v>0.3418679690235156</v>
       </c>
     </row>
     <row r="18">
@@ -1398,19 +1404,19 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>1240952244</v>
+        <v>1347067397</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>419047620</v>
+        <v>424368859</v>
       </c>
       <c r="F18" s="19" t="n">
         <v>34581126</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>453628746</v>
+        <v>458949985</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>0.3655489147090821</v>
+        <v>0.3407030606056602</v>
       </c>
     </row>
     <row r="19">
@@ -1423,19 +1429,19 @@
         </is>
       </c>
       <c r="D19" s="19" t="n">
-        <v>583256268</v>
+        <v>543282274</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>119727891</v>
+        <v>115736962</v>
       </c>
       <c r="F19" s="19" t="n">
         <v>88421641</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>208149532</v>
+        <v>204158603</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>0.3568749166018392</v>
+        <v>0.3757873443888581</v>
       </c>
     </row>
     <row r="20">
@@ -1448,19 +1454,19 @@
         </is>
       </c>
       <c r="D20" s="19" t="n">
-        <v>1161621042</v>
+        <v>1230123482</v>
       </c>
       <c r="E20" s="19" t="n">
-        <v>399092971</v>
+        <v>385789872</v>
       </c>
       <c r="F20" s="19" t="n">
         <v>11234100</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>410327071</v>
+        <v>397023972</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>0.3532366031296461</v>
+        <v>0.3227513154650924</v>
       </c>
     </row>
     <row r="21">
@@ -1473,19 +1479,19 @@
         </is>
       </c>
       <c r="D21" s="19" t="n">
-        <v>864811602</v>
+        <v>735943613</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>219501134</v>
+        <v>212184430</v>
       </c>
       <c r="F21" s="19" t="n">
         <v>79239773</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>298740907</v>
+        <v>291424203</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>0.3454404477334937</v>
+        <v>0.3959871352263505</v>
       </c>
     </row>
     <row r="22">
@@ -1498,7 +1504,7 @@
         </is>
       </c>
       <c r="D22" s="19" t="n">
-        <v>401037884</v>
+        <v>300816749</v>
       </c>
       <c r="E22" s="19" t="n">
         <v>0</v>
@@ -1510,7 +1516,32 @@
         <v>114438802</v>
       </c>
       <c r="H22" s="20" t="n">
-        <v>0.2853565874090838</v>
+        <v>0.3804269621968423</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Võ Thị Hằng</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>1007529600</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>347210885</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>347210885</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>0.3446160638853688</v>
       </c>
     </row>
   </sheetData>
@@ -1542,8 +1573,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:M21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
@@ -1576,18 +1607,15 @@
       <c r="C3" s="22" t="n">
         <v>0.4667</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tổng CH BHX:</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>240</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>TB BHX/CH:</t>
-        </is>
+      <c r="H3" s="2">
+        <f>'Data BHX'!B5</f>
+        <v/>
       </c>
       <c r="I3" s="23" t="n">
         <v>19954649</v>
@@ -1679,10 +1707,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1181190660</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>419047620</v>
+        <v>1224747376</v>
+      </c>
+      <c r="E7" s="27">
+        <f>'Data BHX'!E8</f>
+        <v/>
       </c>
       <c r="F7" s="27" t="n">
         <v>13622532</v>
@@ -1719,10 +1748,11 @@
         </is>
       </c>
       <c r="D8" s="27" t="n">
-        <v>1354847566</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>498866214</v>
+        <v>1553803206</v>
+      </c>
+      <c r="E8" s="27">
+        <f>'Data BHX'!E9</f>
+        <v/>
       </c>
       <c r="F8" s="27" t="n">
         <v>2270422</v>
@@ -1759,10 +1789,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>1399499656</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>498866214</v>
+        <v>1439209643</v>
+      </c>
+      <c r="E9" s="27">
+        <f>'Data BHX'!E10</f>
+        <v/>
       </c>
       <c r="F9" s="27" t="n">
         <v>13622532</v>
@@ -1799,10 +1830,11 @@
         </is>
       </c>
       <c r="D10" s="27" t="n">
-        <v>1240952244</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>419047620</v>
+        <v>1347067397</v>
+      </c>
+      <c r="E10" s="27">
+        <f>'Data BHX'!E11</f>
+        <v/>
       </c>
       <c r="F10" s="27" t="n">
         <v>0</v>
@@ -1839,10 +1871,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>1292631579</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>478911565</v>
+        <v>1490030916</v>
+      </c>
+      <c r="E11" s="27">
+        <f>'Data BHX'!E12</f>
+        <v/>
       </c>
       <c r="F11" s="27" t="n">
         <v>0</v>
@@ -1879,10 +1912,11 @@
         </is>
       </c>
       <c r="D12" s="27" t="n">
-        <v>864811602</v>
-      </c>
-      <c r="E12" s="27" t="n">
-        <v>219501134</v>
+        <v>735943613</v>
+      </c>
+      <c r="E12" s="27">
+        <f>'Data BHX'!E13</f>
+        <v/>
       </c>
       <c r="F12" s="27" t="n">
         <v>54490128</v>
@@ -1919,10 +1953,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>401037884</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>0</v>
+        <v>300816749</v>
+      </c>
+      <c r="E13" s="27">
+        <f>'Data BHX'!E14</f>
+        <v/>
       </c>
       <c r="F13" s="27" t="n">
         <v>45408440</v>
@@ -1959,10 +1994,11 @@
         </is>
       </c>
       <c r="D14" s="27" t="n">
-        <v>1346491228</v>
-      </c>
-      <c r="E14" s="27" t="n">
-        <v>498866214</v>
+        <v>1427158977</v>
+      </c>
+      <c r="E14" s="27">
+        <f>'Data BHX'!E15</f>
+        <v/>
       </c>
       <c r="F14" s="27" t="n">
         <v>0</v>
@@ -1999,10 +2035,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>583256268</v>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>119727891</v>
+        <v>543282274</v>
+      </c>
+      <c r="E15" s="27">
+        <f>'Data BHX'!E16</f>
+        <v/>
       </c>
       <c r="F15" s="27" t="n">
         <v>29515486</v>
@@ -2039,10 +2076,11 @@
         </is>
       </c>
       <c r="D16" s="27" t="n">
-        <v>1161621042</v>
-      </c>
-      <c r="E16" s="27" t="n">
-        <v>399092971</v>
+        <v>1230123482</v>
+      </c>
+      <c r="E16" s="27">
+        <f>'Data BHX'!E17</f>
+        <v/>
       </c>
       <c r="F16" s="27" t="n">
         <v>0</v>
@@ -2070,62 +2108,104 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="B17" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Võ Thị Hằng</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>1007529600</v>
+      </c>
+      <c r="E17" s="27">
+        <f>'Data BHX'!E18</f>
+        <v/>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="28" t="n">
+        <v>359183682</v>
+      </c>
+      <c r="M17" s="29" t="n">
+        <v>0.3564993842364532</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>TỔNG TEAM</t>
         </is>
       </c>
-      <c r="D17" s="32">
-        <f>SUM(D7:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="32">
-        <f>SUM(E7:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>SUM(F7:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="32">
-        <f>SUM(G7:G16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="32">
-        <f>SUM(H7:H16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="32">
-        <f>SUM(I7:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="32">
-        <f>SUM(J7:J16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="32">
-        <f>SUM(K7:K16)</f>
-        <v/>
-      </c>
-      <c r="L17" s="32">
-        <f>SUM(L7:L16)</f>
-        <v/>
-      </c>
-      <c r="M17" s="33">
-        <f>L17/D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="34" t="inlineStr">
+      <c r="D18" s="32">
+        <f>SUM(D7:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>SUM(E7:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>SUM(F7:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="32">
+        <f>SUM(G7:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="32">
+        <f>SUM(H7:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="32">
+        <f>SUM(I7:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="32">
+        <f>SUM(J7:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="32">
+        <f>SUM(K7:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="32">
+        <f>SUM(L7:L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="33">
+        <f>L18/D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>📌 % Đạt ≥ % Timegone (46.7%) → Vượt/Đạt tiến độ 🟢 (#28E11F) | Cận Timegone (35.0% - &lt;46.7%) → Cảnh báo 🟠 (#F5991F) | Thấp hơn nhiều (&lt;35.0%) → Cần đẩy nhanh 🔴 (#DD2323)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="35" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>🧮 BHX cố định = (Tổng BHX ÷ 232) × Số CH phụ trách | Thực Hiện = BHX + GS25 + 7E + FM + CK + HĐ + WMP | % Đạt = TH ÷ Target</t>
         </is>
@@ -2161,8 +2241,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F163"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -6190,16 +6270,87 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="49" t="inlineStr">
+      <c r="A159" s="36" t="inlineStr">
+        <is>
+          <t>👤 Võ Thị Hằng (2 cửa hàng CVS)</t>
+        </is>
+      </c>
+      <c r="E159" s="37" t="inlineStr">
+        <is>
+          <t>TỔNG CVS:</t>
+        </is>
+      </c>
+      <c r="F159" s="109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="39" t="n">
+        <v>139</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Võ Thị Hằng</t>
+        </is>
+      </c>
+      <c r="C160" s="48" t="inlineStr">
+        <is>
+          <t>GS25</t>
+        </is>
+      </c>
+      <c r="D160" s="41" t="inlineStr">
+        <is>
+          <t>CVS_GS25.75.6976</t>
+        </is>
+      </c>
+      <c r="E160" s="41" t="inlineStr">
+        <is>
+          <t>GS25 Lê Duẩn - Long Thành</t>
+        </is>
+      </c>
+      <c r="F160" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="39" t="n">
+        <v>140</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Võ Thị Hằng</t>
+        </is>
+      </c>
+      <c r="C161" s="48" t="inlineStr">
+        <is>
+          <t>GS25</t>
+        </is>
+      </c>
+      <c r="D161" s="41" t="inlineStr">
+        <is>
+          <t>CVS_GS25.75.6975</t>
+        </is>
+      </c>
+      <c r="E161" s="41" t="inlineStr">
+        <is>
+          <t>Siêu thị GS-25 35, Nguyễn Đình Chiểu</t>
+        </is>
+      </c>
+      <c r="F161" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162"/>
+    <row r="163">
+      <c r="A163" s="49" t="inlineStr">
         <is>
           <t>🎯 TỔNG CVS TOÀN TEAM</t>
         </is>
       </c>
-      <c r="F159" s="50" t="n">
+      <c r="F163" s="50" t="n">
         <v>372666880</v>
       </c>
     </row>
-    <row r="162"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A159:D159"/>
@@ -6223,8 +6374,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -6237,7 +6388,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="51" t="inlineStr">
         <is>
-          <t>PHÂN BỔ DOANH SỐ BHX (232 CỬA HÀNG)</t>
+          <t>PHÂN BỔ DOANH SỐ BHX (240 CỬA HÀNG)</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6409,7 @@
         </is>
       </c>
       <c r="B4" s="53" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">
@@ -6320,11 +6471,13 @@
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E8" s="55" t="n">
-        <v>419047620</v>
-      </c>
-      <c r="F8" s="56" t="n">
-        <v>0.09051724137931035</v>
+      <c r="E8" s="55">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="56">
+        <f>E8/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -6337,17 +6490,19 @@
         </is>
       </c>
       <c r="C9" s="26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="55">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E9" s="55" t="n">
-        <v>498866214</v>
-      </c>
-      <c r="F9" s="56" t="n">
-        <v>0.1077586206896552</v>
+      <c r="E9" s="55">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="56">
+        <f>E9/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -6360,17 +6515,19 @@
         </is>
       </c>
       <c r="C10" s="26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="55">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E10" s="55" t="n">
-        <v>498866214</v>
-      </c>
-      <c r="F10" s="56" t="n">
-        <v>0.1077586206896552</v>
+      <c r="E10" s="55">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="56">
+        <f>E10/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -6383,17 +6540,19 @@
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="55">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E11" s="55" t="n">
-        <v>419047620</v>
-      </c>
-      <c r="F11" s="56" t="n">
-        <v>0.09051724137931035</v>
+      <c r="E11" s="55">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="56">
+        <f>E11/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -6406,17 +6565,19 @@
         </is>
       </c>
       <c r="C12" s="26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" s="55">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E12" s="55" t="n">
-        <v>478911565</v>
-      </c>
-      <c r="F12" s="56" t="n">
-        <v>0.103448275862069</v>
+      <c r="E12" s="55">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="56">
+        <f>E12/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -6435,11 +6596,13 @@
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E13" s="55" t="n">
-        <v>219501134</v>
-      </c>
-      <c r="F13" s="56" t="n">
-        <v>0.04741379310344827</v>
+      <c r="E13" s="55">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="56">
+        <f>E13/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -6458,11 +6621,13 @@
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E14" s="55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="56" t="n">
-        <v>0</v>
+      <c r="E14" s="55">
+        <f>C14*D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="56">
+        <f>E14/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -6475,17 +6640,19 @@
         </is>
       </c>
       <c r="C15" s="26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="55">
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E15" s="55" t="n">
-        <v>498866214</v>
-      </c>
-      <c r="F15" s="56" t="n">
-        <v>0.1077586206896552</v>
+      <c r="E15" s="55">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="56">
+        <f>E15/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -6504,11 +6671,13 @@
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E16" s="55" t="n">
-        <v>119727891</v>
-      </c>
-      <c r="F16" s="56" t="n">
-        <v>0.02586206896551724</v>
+      <c r="E16" s="55">
+        <f>C16*D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="56">
+        <f>E16/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -6527,30 +6696,59 @@
         <f>$B$5</f>
         <v/>
       </c>
-      <c r="E17" s="55" t="n">
-        <v>399092971</v>
-      </c>
-      <c r="F17" s="56" t="n">
-        <v>0.08620689655172414</v>
+      <c r="E17" s="55">
+        <f>C17*D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="56">
+        <f>E17/$E$19</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr"/>
-      <c r="B18" s="57" t="inlineStr">
+      <c r="A18" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Võ Thị Hằng</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" s="55">
+        <f>$B$5</f>
+        <v/>
+      </c>
+      <c r="E18" s="55">
+        <f>C18*D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="56">
+        <f>E18/$E$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr"/>
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="C18" s="58" t="n">
-        <v>178</v>
-      </c>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="59">
-        <f>SUM(E8:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="60" t="n">
-        <v>0.7672413793103449</v>
+      <c r="C19" s="26">
+        <f>SUM(C8:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="55" t="n"/>
+      <c r="E19" s="55">
+        <f>SUM(E8:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="56">
+        <f>E19/$B$3</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6568,7 +6766,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -6613,7 +6811,7 @@
       </c>
       <c r="B5" s="61" t="inlineStr">
         <is>
-          <t>9/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6858,7 @@
         </is>
       </c>
       <c r="B9" s="61" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -6670,7 +6868,7 @@
         </is>
       </c>
       <c r="B10" s="61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -6680,7 +6878,7 @@
         </is>
       </c>
       <c r="B11" s="61" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -6709,8 +6907,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:BB41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -6766,7 +6964,6 @@
     <col width="16" customWidth="1" min="52" max="52"/>
     <col width="16" customWidth="1" min="53" max="53"/>
     <col width="16" customWidth="1" min="54" max="54"/>
-    <col width="22" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -6937,11 +7134,6 @@
       <c r="AZ4" s="107" t="n"/>
       <c r="BA4" s="107" t="n"/>
       <c r="BB4" s="108" t="n"/>
-      <c r="BC4" s="108" t="inlineStr">
-        <is>
-          <t>SẢN PHẨM MỚI PHÁT SINH / KHÁC</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="77" t="inlineStr">
@@ -7260,12 +7452,6 @@
 (05BG13)</t>
         </is>
       </c>
-      <c r="BC5" s="86" t="inlineStr">
-        <is>
-          <t>Creamer đặc Ông Thọ vị Matcha tuýp 165g
-(01TM60)</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="87" t="inlineStr">
@@ -7297,7 +7483,7 @@
         <v>2870400</v>
       </c>
       <c r="G6" s="90">
-        <f>SUM(I6:BC6)</f>
+        <f>SUM(I6:BB6)</f>
         <v/>
       </c>
       <c r="H6" s="91">
@@ -7442,9 +7628,6 @@
       <c r="BB6" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="98" t="inlineStr">
@@ -7476,7 +7659,7 @@
         <v>6513600</v>
       </c>
       <c r="G7" s="90">
-        <f>SUM(I7:BC7)</f>
+        <f>SUM(I7:BB7)</f>
         <v/>
       </c>
       <c r="H7" s="91">
@@ -7621,9 +7804,6 @@
       <c r="BB7" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC7" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="87" t="inlineStr">
@@ -7655,7 +7835,7 @@
         <v>8846550</v>
       </c>
       <c r="G8" s="90">
-        <f>SUM(I8:BC8)</f>
+        <f>SUM(I8:BB8)</f>
         <v/>
       </c>
       <c r="H8" s="91">
@@ -7800,9 +7980,6 @@
       <c r="BB8" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="98" t="inlineStr">
@@ -7834,7 +8011,7 @@
         <v>5192250</v>
       </c>
       <c r="G9" s="90">
-        <f>SUM(I9:BC9)</f>
+        <f>SUM(I9:BB9)</f>
         <v/>
       </c>
       <c r="H9" s="91">
@@ -7979,9 +8156,6 @@
       <c r="BB9" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC9" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="87" t="inlineStr">
@@ -8013,7 +8187,7 @@
         <v>6924900</v>
       </c>
       <c r="G10" s="90">
-        <f>SUM(I10:BC10)</f>
+        <f>SUM(I10:BB10)</f>
         <v/>
       </c>
       <c r="H10" s="91">
@@ -8158,9 +8332,6 @@
       <c r="BB10" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC10" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="98" t="inlineStr">
@@ -8192,7 +8363,7 @@
         <v>6491100</v>
       </c>
       <c r="G11" s="90">
-        <f>SUM(I11:BC11)</f>
+        <f>SUM(I11:BB11)</f>
         <v/>
       </c>
       <c r="H11" s="91">
@@ -8337,9 +8508,6 @@
       <c r="BB11" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC11" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="87" t="inlineStr">
@@ -8371,7 +8539,7 @@
         <v>5192250</v>
       </c>
       <c r="G12" s="90">
-        <f>SUM(I12:BC12)</f>
+        <f>SUM(I12:BB12)</f>
         <v/>
       </c>
       <c r="H12" s="91">
@@ -8516,9 +8684,6 @@
       <c r="BB12" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC12" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="98" t="inlineStr">
@@ -8550,7 +8715,7 @@
         <v>7022550</v>
       </c>
       <c r="G13" s="90">
-        <f>SUM(I13:BC13)</f>
+        <f>SUM(I13:BB13)</f>
         <v/>
       </c>
       <c r="H13" s="91">
@@ -8695,9 +8860,6 @@
       <c r="BB13" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC13" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="87" t="inlineStr">
@@ -8729,7 +8891,7 @@
         <v>7731300</v>
       </c>
       <c r="G14" s="90">
-        <f>SUM(I14:BC14)</f>
+        <f>SUM(I14:BB14)</f>
         <v/>
       </c>
       <c r="H14" s="91">
@@ -8874,9 +9036,6 @@
       <c r="BB14" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC14" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="98" t="inlineStr">
@@ -8908,7 +9067,7 @@
         <v>6750450</v>
       </c>
       <c r="G15" s="90">
-        <f>SUM(I15:BC15)</f>
+        <f>SUM(I15:BB15)</f>
         <v/>
       </c>
       <c r="H15" s="91">
@@ -9053,9 +9212,6 @@
       <c r="BB15" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC15" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="87" t="inlineStr">
@@ -9087,7 +9243,7 @@
         <v>12073650</v>
       </c>
       <c r="G16" s="90">
-        <f>SUM(I16:BC16)</f>
+        <f>SUM(I16:BB16)</f>
         <v/>
       </c>
       <c r="H16" s="91">
@@ -9232,9 +9388,6 @@
       <c r="BB16" s="97" t="n">
         <v>129900</v>
       </c>
-      <c r="BC16" s="97" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="98" t="inlineStr">
@@ -9266,7 +9419,7 @@
         <v>6569600</v>
       </c>
       <c r="G17" s="90">
-        <f>SUM(I17:BC17)</f>
+        <f>SUM(I17:BB17)</f>
         <v/>
       </c>
       <c r="H17" s="91">
@@ -9411,9 +9564,6 @@
       <c r="BB17" s="97" t="n">
         <v>129900</v>
       </c>
-      <c r="BC17" s="97" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="87" t="inlineStr">
@@ -9445,7 +9595,7 @@
         <v>13829500</v>
       </c>
       <c r="G18" s="90">
-        <f>SUM(I18:BC18)</f>
+        <f>SUM(I18:BB18)</f>
         <v/>
       </c>
       <c r="H18" s="91">
@@ -9590,9 +9740,6 @@
       <c r="BB18" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC18" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="98" t="inlineStr">
@@ -9624,7 +9771,7 @@
         <v>9678900</v>
       </c>
       <c r="G19" s="90">
-        <f>SUM(I19:BC19)</f>
+        <f>SUM(I19:BB19)</f>
         <v/>
       </c>
       <c r="H19" s="91">
@@ -9769,9 +9916,6 @@
       <c r="BB19" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC19" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="87" t="inlineStr">
@@ -9803,7 +9947,7 @@
         <v>5523600</v>
       </c>
       <c r="G20" s="90">
-        <f>SUM(I20:BC20)</f>
+        <f>SUM(I20:BB20)</f>
         <v/>
       </c>
       <c r="H20" s="91">
@@ -9948,9 +10092,6 @@
       <c r="BB20" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="98" t="inlineStr">
@@ -9982,7 +10123,7 @@
         <v>13829500</v>
       </c>
       <c r="G21" s="90">
-        <f>SUM(I21:BC21)</f>
+        <f>SUM(I21:BB21)</f>
         <v/>
       </c>
       <c r="H21" s="91">
@@ -10127,9 +10268,6 @@
       <c r="BB21" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC21" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="87" t="inlineStr">
@@ -10161,7 +10299,7 @@
         <v>3859200</v>
       </c>
       <c r="G22" s="90">
-        <f>SUM(I22:BC22)</f>
+        <f>SUM(I22:BB22)</f>
         <v/>
       </c>
       <c r="H22" s="91">
@@ -10306,9 +10444,6 @@
       <c r="BB22" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC22" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="98" t="inlineStr">
@@ -10340,7 +10475,7 @@
         <v>3651900</v>
       </c>
       <c r="G23" s="90">
-        <f>SUM(I23:BC23)</f>
+        <f>SUM(I23:BB23)</f>
         <v/>
       </c>
       <c r="H23" s="91">
@@ -10485,9 +10620,6 @@
       <c r="BB23" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="87" t="inlineStr">
@@ -10519,7 +10651,7 @@
         <v>1725000</v>
       </c>
       <c r="G24" s="90">
-        <f>SUM(I24:BC24)</f>
+        <f>SUM(I24:BB24)</f>
         <v/>
       </c>
       <c r="H24" s="91">
@@ -10664,9 +10796,6 @@
       <c r="BB24" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC24" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="98" t="inlineStr">
@@ -10698,7 +10827,7 @@
         <v>6432600</v>
       </c>
       <c r="G25" s="90">
-        <f>SUM(I25:BC25)</f>
+        <f>SUM(I25:BB25)</f>
         <v/>
       </c>
       <c r="H25" s="91">
@@ -10843,9 +10972,6 @@
       <c r="BB25" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC25" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="87" t="inlineStr">
@@ -10877,7 +11003,7 @@
         <v>13433350</v>
       </c>
       <c r="G26" s="90">
-        <f>SUM(I26:BC26)</f>
+        <f>SUM(I26:BB26)</f>
         <v/>
       </c>
       <c r="H26" s="91">
@@ -11022,9 +11148,6 @@
       <c r="BB26" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC26" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="98" t="inlineStr">
@@ -11056,7 +11179,7 @@
         <v>8826000</v>
       </c>
       <c r="G27" s="90">
-        <f>SUM(I27:BC27)</f>
+        <f>SUM(I27:BB27)</f>
         <v/>
       </c>
       <c r="H27" s="91">
@@ -11201,9 +11324,6 @@
       <c r="BB27" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC27" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="87" t="inlineStr">
@@ -11235,7 +11355,7 @@
         <v>29534600</v>
       </c>
       <c r="G28" s="90">
-        <f>SUM(I28:BC28)</f>
+        <f>SUM(I28:BB28)</f>
         <v/>
       </c>
       <c r="H28" s="91">
@@ -11380,9 +11500,6 @@
       <c r="BB28" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC28" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="98" t="inlineStr">
@@ -11414,7 +11531,7 @@
         <v>5475750</v>
       </c>
       <c r="G29" s="90">
-        <f>SUM(I29:BC29)</f>
+        <f>SUM(I29:BB29)</f>
         <v/>
       </c>
       <c r="H29" s="91">
@@ -11559,9 +11676,6 @@
       <c r="BB29" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC29" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="87" t="inlineStr">
@@ -11593,7 +11707,7 @@
         <v>5920200</v>
       </c>
       <c r="G30" s="90">
-        <f>SUM(I30:BC30)</f>
+        <f>SUM(I30:BB30)</f>
         <v/>
       </c>
       <c r="H30" s="91">
@@ -11738,9 +11852,6 @@
       <c r="BB30" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC30" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="98" t="inlineStr">
@@ -11772,7 +11883,7 @@
         <v>2947500</v>
       </c>
       <c r="G31" s="90">
-        <f>SUM(I31:BC31)</f>
+        <f>SUM(I31:BB31)</f>
         <v/>
       </c>
       <c r="H31" s="91">
@@ -11917,9 +12028,6 @@
       <c r="BB31" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC31" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="87" t="inlineStr">
@@ -11951,7 +12059,7 @@
         <v>3131550</v>
       </c>
       <c r="G32" s="90">
-        <f>SUM(I32:BC32)</f>
+        <f>SUM(I32:BB32)</f>
         <v/>
       </c>
       <c r="H32" s="91">
@@ -12096,9 +12204,6 @@
       <c r="BB32" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC32" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="98" t="inlineStr">
@@ -12130,7 +12235,7 @@
         <v>9255800</v>
       </c>
       <c r="G33" s="90">
-        <f>SUM(I33:BC33)</f>
+        <f>SUM(I33:BB33)</f>
         <v/>
       </c>
       <c r="H33" s="91">
@@ -12275,9 +12380,6 @@
       <c r="BB33" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC33" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="87" t="inlineStr">
@@ -12309,7 +12411,7 @@
         <v>15527400</v>
       </c>
       <c r="G34" s="90">
-        <f>SUM(I34:BC34)</f>
+        <f>SUM(I34:BB34)</f>
         <v/>
       </c>
       <c r="H34" s="91">
@@ -12454,9 +12556,6 @@
       <c r="BB34" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC34" s="93" t="n">
-        <v>274800</v>
-      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="98" t="inlineStr">
@@ -12488,7 +12587,7 @@
         <v>7526550</v>
       </c>
       <c r="G35" s="90">
-        <f>SUM(I35:BC35)</f>
+        <f>SUM(I35:BB35)</f>
         <v/>
       </c>
       <c r="H35" s="91">
@@ -12633,9 +12732,6 @@
       <c r="BB35" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="87" t="inlineStr">
@@ -12667,7 +12763,7 @@
         <v>11488300</v>
       </c>
       <c r="G36" s="90">
-        <f>SUM(I36:BC36)</f>
+        <f>SUM(I36:BB36)</f>
         <v/>
       </c>
       <c r="H36" s="91">
@@ -12812,9 +12908,6 @@
       <c r="BB36" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC36" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="98" t="inlineStr">
@@ -12846,7 +12939,7 @@
         <v>4002600</v>
       </c>
       <c r="G37" s="90">
-        <f>SUM(I37:BC37)</f>
+        <f>SUM(I37:BB37)</f>
         <v/>
       </c>
       <c r="H37" s="91">
@@ -12991,9 +13084,6 @@
       <c r="BB37" s="100" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" s="100" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="87" t="inlineStr">
@@ -13025,7 +13115,7 @@
         <v>7843700</v>
       </c>
       <c r="G38" s="90">
-        <f>SUM(I38:BC38)</f>
+        <f>SUM(I38:BB38)</f>
         <v/>
       </c>
       <c r="H38" s="91">
@@ -13170,9 +13260,6 @@
       <c r="BB38" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="BC38" s="93" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="98" t="inlineStr">
@@ -13204,7 +13291,7 @@
         <v>6062450</v>
       </c>
       <c r="G39" s="90">
-        <f>SUM(I39:BC39)</f>
+        <f>SUM(I39:BB39)</f>
         <v/>
       </c>
       <c r="H39" s="91">
@@ -13347,9 +13434,6 @@
         <v>0</v>
       </c>
       <c r="BB39" s="100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" s="100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13375,7 +13459,7 @@
         <v>16302700</v>
       </c>
       <c r="G40" s="90">
-        <f>SUM(I40:BC40)</f>
+        <f>SUM(I40:BB40)</f>
         <v/>
       </c>
       <c r="H40" s="91">
@@ -13518,9 +13602,6 @@
         <v>0</v>
       </c>
       <c r="BB40" s="93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" s="93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13728,10 +13809,6 @@
       </c>
       <c r="BB41" s="106">
         <f>SUBTOTAL(9, BB6:BB40)</f>
-        <v/>
-      </c>
-      <c r="BC41" s="106">
-        <f>SUBTOTAL(9, BC6:BC40)</f>
         <v/>
       </c>
     </row>
